--- a/files/Disciplinary_Cases.xlsx
+++ b/files/Disciplinary_Cases.xlsx
@@ -464,7 +464,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N51"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
